--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487782_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487782_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6171</v>
+        <v>3.9337</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4734</v>
+        <v>3.4671</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1437</v>
+        <v>0.4666</v>
       </c>
       <c r="G2" t="n">
         <v>1.1438</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8083</v>
+        <v>0.1249</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0992</v>
+        <v>0.0929</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.291</v>
+        <v>0.032</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9661</v>
+        <v>2.0756</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1169</v>
+        <v>1.9788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8492</v>
+        <v>0.0968</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.5831</v>
+        <v>-0.2493</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0621</v>
+        <v>1.5436</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.521</v>
+        <v>-1.7929</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.8114</v>
+        <v>0.4774</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2863</v>
+        <v>1.4539</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5251</v>
+        <v>-0.9765</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7267</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7758</v>
+        <v>0.0897</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0041</v>
+        <v>-0.8164</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7607</v>
+        <v>0.1039</v>
       </c>
       <c r="U3" t="n">
-        <v>0.291</v>
+        <v>-0.0496</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7205</v>
+        <v>1.8505</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7411</v>
+        <v>2.9202</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0206</v>
+        <v>-1.0697</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2493</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5436</v>
+        <v>0.2666</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7929</v>
+        <v>0.3347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4774</v>
+        <v>2.4344</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4539</v>
+        <v>1.569</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9765</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7267</v>
+        <v>-1.8331</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0897</v>
+        <v>-1.3025</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8164</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3008</v>
+        <v>0.0442</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1338</v>
+        <v>0.4858</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.167</v>
+        <v>-0.4416</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8137</v>
+        <v>-0.4599</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4286</v>
+        <v>1.5935</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4105</v>
+        <v>1.9277</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0181</v>
+        <v>-0.3342</v>
       </c>
       <c r="G5" t="n">
         <v>0.0508</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0261</v>
+        <v>0.191</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6042</v>
+        <v>0.2519</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9376</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2407</v>
+        <v>0.9625</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1049</v>
+        <v>0.3482</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8642</v>
+        <v>0.6143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6012999999999999</v>
+        <v>-2.5831</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2666</v>
+        <v>-1.0621</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3347</v>
+        <v>-1.521</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4344</v>
+        <v>-1.8114</v>
       </c>
       <c r="K6" t="n">
-        <v>1.569</v>
+        <v>-0.2863</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8653999999999999</v>
+        <v>-1.5251</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8331</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3025</v>
+        <v>-0.7758</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.0041</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>2.4974</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>2.4974</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5656</v>
+        <v>1.0482</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3295</v>
+        <v>0.9921</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2361</v>
+        <v>0.0562</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4599</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5088</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2418</v>
+        <v>0.158</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7506</v>
+        <v>-0.6625</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7599</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2511</v>
+        <v>0.2554</v>
       </c>
       <c r="T7" t="n">
-        <v>1.295</v>
+        <v>1.2111</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0438</v>
+        <v>-0.9557</v>
       </c>
       <c r="V7" t="n">
         <v>0.5838</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7513</v>
+        <v>-0.9656</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3675</v>
+        <v>1.1532</v>
       </c>
       <c r="F8" t="n">
         <v>-2.1188</v>
@@ -1078,10 +1078,10 @@
         <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0248</v>
+        <v>-0.1895</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="U8" t="n">
         <v>-0.5715</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7647</v>
+        <v>-1.433</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0556</v>
+        <v>0.2699</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8203</v>
+        <v>-1.7029</v>
       </c>
       <c r="G9" t="n">
         <v>-0.247</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3908</v>
+        <v>-0.059</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3882</v>
+        <v>0.6025</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.779</v>
+        <v>-0.6615</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7513</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7971</v>
+        <v>-5.1117</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4423</v>
+        <v>-4.6689</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3548</v>
+        <v>-0.4429</v>
       </c>
       <c r="G10" t="n">
         <v>-4.779</v>
@@ -1234,13 +1234,13 @@
         <v>2.4974</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3074</v>
+        <v>-0.6221</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2925</v>
+        <v>-0.5191</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.015</v>
+        <v>-0.103</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5892</v>
+        <v>-5.8604</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3993</v>
+        <v>-3.9054</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1899</v>
+        <v>-1.955</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6146</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2877</v>
+        <v>0.441</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2048</v>
+        <v>0.6987</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4925</v>
+        <v>-0.2577</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.438100000000002</v>
+        <v>-3.459400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.670100000000001</v>
+        <v>3.6488</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.1082</v>
+        <v>-7.1083</v>
       </c>
       <c r="G12" t="n">
         <v>-10.8374</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7559000000000007</v>
+        <v>0.7559000000000002</v>
       </c>
       <c r="I12" t="n">
         <v>-11.5932</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9571999999999998</v>
+        <v>-0.9572000000000007</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1458</v>
+        <v>5.145799999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-6.1028</v>
@@ -1378,7 +1378,7 @@
         <v>-4.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.4904</v>
+        <v>-5.490399999999999</v>
       </c>
       <c r="P12" t="n">
         <v>10.4058</v>
@@ -1390,13 +1390,13 @@
         <v>15.6088</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3098000000000001</v>
+        <v>1.2884</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0103</v>
+        <v>3.989</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7007</v>
+        <v>-2.7005</v>
       </c>
       <c r="V12" t="n">
         <v>-4.3163</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>J. JERMAIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1349</v>
+        <v>7.3886</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4148</v>
+        <v>7.0626</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7201</v>
+        <v>0.326</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5915</v>
+        <v>7.5356</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8592</v>
+        <v>1.4181</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7323</v>
+        <v>6.1175</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6446</v>
+        <v>7.2175</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4878</v>
+        <v>1.8185</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1568</v>
+        <v>5.399</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9469</v>
+        <v>0.3181</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3713</v>
+        <v>-0.4004</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5756</v>
+        <v>0.7185</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R13" t="n">
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>3.354</v>
+        <v>-0.7546</v>
       </c>
       <c r="T13" t="n">
-        <v>4.0377</v>
+        <v>-0.1819</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6837</v>
+        <v>-0.5727</v>
       </c>
       <c r="V13" t="n">
-        <v>0.23</v>
+        <v>2.6889</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8137</v>
+        <v>3.1488</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JERMAIN</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6512</v>
+        <v>4.91</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5268</v>
+        <v>4.1645</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1244</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5356</v>
+        <v>4.5915</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4181</v>
+        <v>3.8592</v>
       </c>
       <c r="I14" t="n">
-        <v>6.1175</v>
+        <v>0.7323</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2175</v>
+        <v>3.6446</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8185</v>
+        <v>3.4878</v>
       </c>
       <c r="L14" t="n">
-        <v>5.399</v>
+        <v>0.1568</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3181</v>
+        <v>0.9469</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4004</v>
+        <v>0.3713</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7185</v>
+        <v>0.5756</v>
       </c>
       <c r="P14" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-2.0812</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-3.1218</v>
       </c>
       <c r="R14" t="n">
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.492</v>
+        <v>1.1292</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>1.7874</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7743</v>
+        <v>-0.6582</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6889</v>
+        <v>0.23</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1488</v>
+        <v>0.8137</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4599</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1096</v>
+        <v>1.3929</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2677</v>
+        <v>1.3749</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1582</v>
+        <v>0.018</v>
       </c>
       <c r="G15" t="n">
         <v>4.1076</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7274</v>
+        <v>-0.4441</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3138</v>
+        <v>-0.2067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4136</v>
+        <v>-0.2374</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8137</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.97</v>
+        <v>1.004</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0142</v>
+        <v>-0.4979</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0441</v>
+        <v>1.5018</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.4039</v>
+        <v>1.8162</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7931</v>
+        <v>1.1663</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6108</v>
+        <v>0.6499</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.7586</v>
+        <v>0.6732</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3926</v>
+        <v>0.5948</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.366</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6453</v>
+        <v>1.143</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4005</v>
+        <v>0.5715</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7552</v>
+        <v>0.5715</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6851</v>
+        <v>-0.1879</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8539</v>
+        <v>-0.1305</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1689</v>
+        <v>-0.0574</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2726</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9198</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4979</v>
+        <v>0.997</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4177</v>
+        <v>-0.0267</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8162</v>
+        <v>2.8399</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1663</v>
+        <v>-3.1575</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6499</v>
+        <v>5.9974</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6732</v>
+        <v>3.2445</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5948</v>
+        <v>-1.6059</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>4.8504</v>
       </c>
       <c r="M17" t="n">
-        <v>1.143</v>
+        <v>-0.4046</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5715</v>
+        <v>-1.5516</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5715</v>
+        <v>1.1471</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.272</v>
+        <v>0.1679</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1305</v>
+        <v>0.4144</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1416</v>
+        <v>-0.2465</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2584</v>
+        <v>0.9661</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4613</v>
+        <v>1.0142</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2029</v>
+        <v>-0.048</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8399</v>
+        <v>-3.4039</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1575</v>
+        <v>-1.7931</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9974</v>
+        <v>-1.6108</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2445</v>
+        <v>-2.7586</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6059</v>
+        <v>-0.3926</v>
       </c>
       <c r="L18" t="n">
-        <v>4.8504</v>
+        <v>-2.366</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4046</v>
+        <v>-0.6453</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5516</v>
+        <v>-1.4005</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1471</v>
+        <v>0.7552</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5441</v>
+        <v>0.6811</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1214</v>
+        <v>0.8539</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4227</v>
+        <v>-0.1728</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4599</v>
+        <v>3.2726</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4599</v>
+        <v>2.9188</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.167</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0435</v>
+        <v>0.7066</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1236</v>
+        <v>-1.3291</v>
       </c>
       <c r="G19" t="n">
         <v>1.0944</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4071</v>
+        <v>0.1375</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5219</v>
+        <v>0.2281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1149</v>
+        <v>-0.0906</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8137</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3554</v>
+        <v>-2.2482</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4025</v>
       </c>
       <c r="F20" t="n">
         <v>-1.8458</v>
@@ -2014,10 +2014,10 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6244</v>
+        <v>-0.5172</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U20" t="n">
         <v>-0.0372</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5142</v>
+        <v>-4.1533</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7024</v>
+        <v>-4.6088</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8118</v>
+        <v>0.4555</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0566</v>
+        <v>-2.9157</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7634</v>
+        <v>-1.616</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2932</v>
+        <v>-1.2998</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1337</v>
+        <v>-4.2666</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2649</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8688</v>
+        <v>-3.3367</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9229000000000001</v>
+        <v>1.3509</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4985</v>
+        <v>-0.6861</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5756</v>
+        <v>2.037</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1449</v>
+        <v>-0.0107</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0743</v>
+        <v>0.3415</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.3522</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5692</v>
+        <v>-4.4555</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8231</v>
+        <v>-2.7024</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2539</v>
+        <v>-1.7531</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9157</v>
+        <v>-4.0566</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.616</v>
+        <v>-2.7634</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2998</v>
+        <v>-1.2932</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.2666</v>
+        <v>-3.1337</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.2649</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.3367</v>
+        <v>-1.8688</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3509</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6861</v>
+        <v>-1.4985</v>
       </c>
       <c r="O22" t="n">
-        <v>2.037</v>
+        <v>0.5756</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4568</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4266</v>
+        <v>0.2036</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1272</v>
+        <v>0.0743</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5538</v>
+        <v>0.1292</v>
       </c>
       <c r="V22" t="n">
         <v>0.23</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.4381</v>
+        <v>5.152400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>7.1083</v>
+        <v>7.108200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.670300000000001</v>
+        <v>-1.9559</v>
       </c>
       <c r="G23" t="n">
         <v>10.8374</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7560999999999996</v>
+        <v>-0.7560999999999987</v>
       </c>
       <c r="I23" t="n">
         <v>11.5931</v>
@@ -2227,10 +2227,10 @@
         <v>4.3897</v>
       </c>
       <c r="L23" t="n">
-        <v>5.490499999999999</v>
+        <v>5.490499999999997</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9569999999999996</v>
+        <v>0.9569999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-5.145799999999999</v>
@@ -2248,22 +2248,22 @@
         <v>5.202999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3095999999999998</v>
+        <v>0.4047999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7006</v>
+        <v>2.7005</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.0104</v>
+        <v>-2.2958</v>
       </c>
       <c r="V23" t="n">
-        <v>4.316500000000001</v>
+        <v>4.3165</v>
       </c>
       <c r="W23" t="n">
         <v>10.1362</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.819800000000001</v>
+        <v>-5.819799999999999</v>
       </c>
     </row>
   </sheetData>
